--- a/data/argentina/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/argentina/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,95 +448,95 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>noM4eJv9</t>
+          <t>fotMKZ7K</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nkx6zI2q</t>
+          <t>YHCv8dOE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pdWqnF1e</t>
+          <t>llkWcC07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vq1qlyXr</t>
+          <t>hMeNaYVf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U9B9fwfF</t>
+          <t>trGn6zgR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -558,95 +558,95 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KvUIXFn2</t>
+          <t>badJ0EGl</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bPuAZyIk</t>
+          <t>2iHr7GwL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tlVEYeXe</t>
+          <t>WCfRbho1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xzFHhHOR</t>
+          <t>vJVmoZG1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rDFDgc9L</t>
+          <t>fRDz9x98</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,68 +656,68 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>U9kvubfS</t>
+          <t>hMZipgW7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jJjztvuM</t>
+          <t>nPhF1f1r</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8fN0daP2</t>
+          <t>trxILFhE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -727,51 +727,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>65Xumenk</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
+          <t>Y9EiyTMr</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SvlzcWFD</t>
+          <t>fgvPVMI8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ngdGLTFj</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
